--- a/jyx2/Assets/Mods/shendiao/Configs/战斗.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/战斗.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="25831"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\jynew\jyx2\Assets\Mods\SAMPLE\Configs\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B607F26-865E-4F27-8739-EA41C71F091A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="3640" yWindow="3640" windowWidth="19140" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="战斗数据" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+  <si>
+    <t>LuaConfigGen</t>
+  </si>
+  <si>
+    <t>Battle</t>
+  </si>
   <si>
     <t>编号</t>
   </si>
@@ -37,6 +37,48 @@
     <t>音乐</t>
   </si>
   <si>
+    <t>队友</t>
+  </si>
+  <si>
+    <t>自动队友</t>
+  </si>
+  <si>
+    <t>敌人</t>
+  </si>
+  <si>
+    <t>L_number</t>
+  </si>
+  <si>
+    <t>L_string</t>
+  </si>
+  <si>
+    <t>L_number[]</t>
+  </si>
+  <si>
+    <t>Id</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>MapScene</t>
+  </si>
+  <si>
+    <t>Exp</t>
+  </si>
+  <si>
+    <t>Music</t>
+  </si>
+  <si>
+    <t>TeamMates</t>
+  </si>
+  <si>
+    <t>AutoTeamMates</t>
+  </si>
+  <si>
+    <t>Enemies</t>
+  </si>
+  <si>
     <t>斗何云多</t>
   </si>
   <si>
@@ -88,24 +130,7 @@
     <t>双飞练武</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1,42</t>
-    </r>
+    <t>41,42</t>
   </si>
   <si>
     <t>斗王远</t>
@@ -183,33 +208,7 @@
     <t>斗毒蛇</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>7</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_Battle</t>
-    </r>
+    <t>07_Battle</t>
   </si>
   <si>
     <t>180,181</t>
@@ -221,61 +220,15 @@
     <t>比武招亲</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>0</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>_Battle</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>90</t>
-    </r>
+    <t>09_Battle</t>
+  </si>
+  <si>
+    <t>190</t>
   </si>
   <si>
     <t>66</t>
   </si>
   <si>
-    <t>09_Battle</t>
-  </si>
-  <si>
     <t>71</t>
   </si>
   <si>
@@ -285,121 +238,56 @@
     <t>22</t>
   </si>
   <si>
-    <t>LuaConfigGen</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Battle</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>队友</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>自动队友</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>敌人</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>L_number</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>L_string</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>L_number[]</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Name</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapScene</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Exp</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Music</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>TeamMates</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>AutoTeamMates</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>Enemies</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <t>斗鹿清笃</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>斗赵志敬</t>
+  </si>
+  <si>
+    <t>斗武氏兄弟</t>
+  </si>
+  <si>
+    <t>斗李莫愁</t>
+  </si>
+  <si>
+    <t>70,71,72</t>
+  </si>
+  <si>
+    <t>斗欧阳锋</t>
+  </si>
+  <si>
+    <t>斗全真群道</t>
+  </si>
+  <si>
+    <t>斗神雕</t>
+  </si>
+  <si>
+    <t>-1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <fonts count="1">
     <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color indexed="8"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -422,40 +310,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <mruColors>
-      <color rgb="FF000000"/>
-    </mruColors>
-  </colors>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -465,39 +332,39 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -529,7 +396,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -564,7 +430,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -576,131 +441,160 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -711,112 +605,105 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H31"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="18.6328125" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" customWidth="1"/>
-    <col min="6" max="6" width="9.1796875" customWidth="1"/>
-    <col min="7" max="7" width="10.54296875" customWidth="1"/>
-    <col min="8" max="8" width="91" style="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:H38"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" ht="13" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="C2" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="13" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>64</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="D4" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>71</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>10</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>5</v>
+      <c r="B5" t="s">
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D5">
         <v>1000</v>
@@ -830,19 +717,19 @@
       <c r="G5">
         <v>0</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6">
         <v>20</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
+      <c r="B6" t="s">
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D6">
         <v>1500</v>
@@ -856,19 +743,19 @@
       <c r="G6">
         <v>0</v>
       </c>
-      <c r="H6" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7">
         <v>21</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>10</v>
+      <c r="B7" t="s">
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="D7">
         <v>1500</v>
@@ -880,21 +767,21 @@
         <v>-1</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+        <v>27</v>
+      </c>
+      <c r="H7" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8">
         <v>30</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>13</v>
+      <c r="B8" t="s">
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>2000</v>
@@ -908,19 +795,19 @@
       <c r="G8">
         <v>-1</v>
       </c>
-      <c r="H8" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9">
         <v>31</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>16</v>
+      <c r="B9" t="s">
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D9">
         <v>1000</v>
@@ -934,19 +821,19 @@
       <c r="G9">
         <v>0</v>
       </c>
-      <c r="H9" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>18</v>
+      <c r="B10" t="s">
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D10">
         <v>1500</v>
@@ -960,19 +847,19 @@
       <c r="G10">
         <v>-1</v>
       </c>
-      <c r="H10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>21</v>
+      <c r="B11" t="s">
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="D11">
         <v>2000</v>
@@ -986,19 +873,19 @@
       <c r="G11">
         <v>-1</v>
       </c>
-      <c r="H11" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12">
         <v>60</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>23</v>
+      <c r="B12" t="s">
+        <v>39</v>
       </c>
       <c r="C12" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="D12">
         <v>3000</v>
@@ -1012,19 +899,19 @@
       <c r="G12">
         <v>-1</v>
       </c>
-      <c r="H12" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13">
         <v>61</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>26</v>
+      <c r="B13" t="s">
+        <v>42</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="D13">
         <v>3000</v>
@@ -1038,19 +925,19 @@
       <c r="G13">
         <v>-1</v>
       </c>
-      <c r="H13" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14">
         <v>70</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>29</v>
+      <c r="B14" t="s">
+        <v>45</v>
       </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="D14">
         <v>1000</v>
@@ -1064,19 +951,19 @@
       <c r="G14">
         <v>-1</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15">
         <v>90</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>32</v>
+      <c r="B15" t="s">
+        <v>48</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D15">
         <v>1000</v>
@@ -1090,19 +977,19 @@
       <c r="G15">
         <v>-1</v>
       </c>
-      <c r="H15" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
       <c r="A16">
         <v>140</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>35</v>
+      <c r="B16" t="s">
+        <v>51</v>
       </c>
       <c r="C16" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D16">
         <v>1000</v>
@@ -1116,19 +1003,19 @@
       <c r="G16">
         <v>-1</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17">
         <v>141</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>35</v>
+      <c r="B17" t="s">
+        <v>51</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D17">
         <v>1000</v>
@@ -1142,19 +1029,19 @@
       <c r="G17">
         <v>-1</v>
       </c>
-      <c r="H17" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18">
         <v>142</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>35</v>
+      <c r="B18" t="s">
+        <v>51</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="D18">
         <v>2000</v>
@@ -1168,19 +1055,19 @@
       <c r="G18">
         <v>-1</v>
       </c>
-      <c r="H18" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19">
         <v>160</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>39</v>
+      <c r="B19" t="s">
+        <v>55</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D19">
         <v>1500</v>
@@ -1194,19 +1081,19 @@
       <c r="G19">
         <v>-1</v>
       </c>
-      <c r="H19" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H19" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>161</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
+      <c r="B20" t="s">
+        <v>55</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D20">
         <v>1500</v>
@@ -1220,19 +1107,19 @@
       <c r="G20">
         <v>-1</v>
       </c>
-      <c r="H20" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H20" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21">
         <v>162</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>39</v>
+      <c r="B21" t="s">
+        <v>55</v>
       </c>
       <c r="C21" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D21">
         <v>1500</v>
@@ -1246,19 +1133,19 @@
       <c r="G21">
         <v>-1</v>
       </c>
-      <c r="H21" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22">
         <v>163</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>39</v>
+      <c r="B22" t="s">
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D22">
         <v>1500</v>
@@ -1272,19 +1159,19 @@
       <c r="G22">
         <v>-1</v>
       </c>
-      <c r="H22" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H22" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23">
         <v>164</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>39</v>
+      <c r="B23" t="s">
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D23">
         <v>1500</v>
@@ -1298,19 +1185,19 @@
       <c r="G23">
         <v>-1</v>
       </c>
-      <c r="H23" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24">
         <v>165</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>45</v>
+      <c r="B24" t="s">
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D24">
         <v>2000</v>
@@ -1324,19 +1211,19 @@
       <c r="G24">
         <v>-1</v>
       </c>
-      <c r="H24" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25">
         <v>180</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>47</v>
+      <c r="B25" t="s">
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D25">
         <v>1000</v>
@@ -1350,19 +1237,19 @@
       <c r="G25">
         <v>-1</v>
       </c>
-      <c r="H25" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26">
         <v>181</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>47</v>
+      <c r="B26" t="s">
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="D26">
         <v>1500</v>
@@ -1376,19 +1263,19 @@
       <c r="G26">
         <v>-1</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H26" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27">
         <v>190</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>52</v>
+      <c r="B27" t="s">
+        <v>67</v>
+      </c>
+      <c r="C27" t="s">
+        <v>68</v>
       </c>
       <c r="D27">
         <v>2000</v>
@@ -1402,19 +1289,19 @@
       <c r="G27">
         <v>11</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H27" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28">
         <v>191</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>52</v>
+      <c r="B28" t="s">
+        <v>67</v>
+      </c>
+      <c r="C28" t="s">
+        <v>68</v>
       </c>
       <c r="D28">
         <v>2000</v>
@@ -1428,19 +1315,19 @@
       <c r="G28">
         <v>11</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29">
         <v>192</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>55</v>
+      <c r="B29" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" t="s">
+        <v>68</v>
       </c>
       <c r="D29">
         <v>2000</v>
@@ -1454,19 +1341,19 @@
       <c r="G29">
         <v>11</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H29" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30">
         <v>193</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>52</v>
+      <c r="B30" t="s">
+        <v>67</v>
+      </c>
+      <c r="C30" t="s">
+        <v>68</v>
       </c>
       <c r="D30">
         <v>2000</v>
@@ -1480,19 +1367,19 @@
       <c r="G30">
         <v>11</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="13" x14ac:dyDescent="0.25">
+      <c r="H30" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31">
         <v>194</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>52</v>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>68</v>
       </c>
       <c r="D31">
         <v>2000</v>
@@ -1506,14 +1393,193 @@
       <c r="G31">
         <v>11</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>58</v>
+      <c r="H31" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32">
+        <v>200</v>
+      </c>
+      <c r="B32" t="s">
+        <v>74</v>
+      </c>
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32">
+        <v>1200</v>
+      </c>
+      <c r="E32">
+        <v>23</v>
+      </c>
+      <c r="F32">
+        <v>-1</v>
+      </c>
+      <c r="G32" t="s">
+        <v>75</v>
+      </c>
+      <c r="H32" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33">
+        <v>201</v>
+      </c>
+      <c r="B33" t="s">
+        <v>77</v>
+      </c>
+      <c r="C33" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33">
+        <v>2000</v>
+      </c>
+      <c r="E33">
+        <v>23</v>
+      </c>
+      <c r="F33">
+        <v>-1</v>
+      </c>
+      <c r="G33">
+        <v>0</v>
+      </c>
+      <c r="H33" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34">
+        <v>202</v>
+      </c>
+      <c r="B34" t="s">
+        <v>78</v>
+      </c>
+      <c r="C34" t="s">
+        <v>22</v>
+      </c>
+      <c r="D34">
+        <v>800</v>
+      </c>
+      <c r="E34">
+        <v>23</v>
+      </c>
+      <c r="F34">
+        <v>-1</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35">
+        <v>203</v>
+      </c>
+      <c r="B35" t="s">
+        <v>79</v>
+      </c>
+      <c r="C35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35">
+        <v>3000</v>
+      </c>
+      <c r="E35">
+        <v>23</v>
+      </c>
+      <c r="F35">
+        <v>-1</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36">
+        <v>204</v>
+      </c>
+      <c r="B36" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36">
+        <v>4000</v>
+      </c>
+      <c r="E36">
+        <v>23</v>
+      </c>
+      <c r="F36">
+        <v>-1</v>
+      </c>
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37">
+        <v>205</v>
+      </c>
+      <c r="B37" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" t="s">
+        <v>35</v>
+      </c>
+      <c r="D37">
+        <v>1500</v>
+      </c>
+      <c r="E37">
+        <v>23</v>
+      </c>
+      <c r="F37">
+        <v>-1</v>
+      </c>
+      <c r="G37">
+        <v>0</v>
+      </c>
+      <c r="H37" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>206</v>
+      </c>
+      <c r="B38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C38" t="s">
+        <v>35</v>
+      </c>
+      <c r="D38">
+        <v>3500</v>
+      </c>
+      <c r="E38">
+        <v>23</v>
+      </c>
+      <c r="F38" t="s">
+        <v>84</v>
+      </c>
+      <c r="G38" t="s">
+        <v>85</v>
+      </c>
+      <c r="H38" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter scaleWithDoc="0" alignWithMargins="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/jyx2/Assets/Mods/shendiao/Configs/战斗.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/战斗.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
   <si>
     <t>LuaConfigGen</t>
   </si>
@@ -275,6 +275,12 @@
   </si>
   <si>
     <t>24</t>
+  </si>
+  <si>
+    <t>斗公孙止</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
 </sst>
 </file>
@@ -606,7 +612,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1579,6 +1585,32 @@
         <v>86</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39">
+        <v>207</v>
+      </c>
+      <c r="B39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" t="s">
+        <v>49</v>
+      </c>
+      <c r="D39">
+        <v>3800</v>
+      </c>
+      <c r="E39">
+        <v>23</v>
+      </c>
+      <c r="F39" t="s">
+        <v>84</v>
+      </c>
+      <c r="G39" t="s">
+        <v>85</v>
+      </c>
+      <c r="H39" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/jyx2/Assets/Mods/shendiao/Configs/战斗.xlsx
+++ b/jyx2/Assets/Mods/shendiao/Configs/战斗.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="91">
   <si>
     <t>LuaConfigGen</t>
   </si>
@@ -281,6 +281,12 @@
   </si>
   <si>
     <t>26</t>
+  </si>
+  <si>
+    <t>斗裘千仞</t>
+  </si>
+  <si>
+    <t>39</t>
   </si>
 </sst>
 </file>
@@ -612,7 +618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1611,6 +1617,32 @@
         <v>88</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40">
+        <v>208</v>
+      </c>
+      <c r="B40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40">
+        <v>4200</v>
+      </c>
+      <c r="E40">
+        <v>23</v>
+      </c>
+      <c r="F40" t="s">
+        <v>84</v>
+      </c>
+      <c r="G40" t="s">
+        <v>85</v>
+      </c>
+      <c r="H40" t="s">
+        <v>90</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
